--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2022.xlsx
@@ -15267,7 +15267,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tasa de matrícula población de 0 a 24 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2022.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2022.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="706">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1297,15 +1297,6 @@
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica y Parinacota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">4304</t>
   </si>
   <si>
@@ -2098,7 +2089,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:36</t>
+    <t xml:space="preserve">2026-09-07 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2510,7 +2501,7 @@
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -8957,16 +8948,16 @@
         <v>2022</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D202" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="E202" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>392</v>
@@ -8978,7 +8969,7 @@
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>75.81</v>
+        <v>75.39</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -8989,16 +8980,16 @@
         <v>2022</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D203" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E203" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>392</v>
@@ -9010,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>75.39</v>
+        <v>75.32</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -9021,16 +9012,16 @@
         <v>2022</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="D204" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>392</v>
@@ -9042,7 +9033,7 @@
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>75.32</v>
+        <v>75.31</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -9053,16 +9044,16 @@
         <v>2022</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="D205" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E205" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>392</v>
@@ -9074,7 +9065,7 @@
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>75.31</v>
+        <v>75.02</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>15</v>
@@ -9085,16 +9076,16 @@
         <v>2022</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D206" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>392</v>
@@ -9106,7 +9097,7 @@
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>75.02</v>
+        <v>74.59</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>15</v>
@@ -9117,16 +9108,16 @@
         <v>2022</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>392</v>
@@ -9138,7 +9129,7 @@
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>74.59</v>
+        <v>74.51</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>15</v>
@@ -9149,16 +9140,16 @@
         <v>2022</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>392</v>
@@ -9170,7 +9161,7 @@
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>74.51</v>
+        <v>74.12</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>15</v>
@@ -9187,10 +9178,10 @@
         <v>394</v>
       </c>
       <c r="D209" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>392</v>
@@ -9202,7 +9193,7 @@
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>74.12</v>
+        <v>73.16</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>15</v>
@@ -9219,10 +9210,10 @@
         <v>394</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>392</v>
@@ -9234,7 +9225,7 @@
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>73.16</v>
+        <v>73.11</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>15</v>
@@ -9245,16 +9236,16 @@
         <v>2022</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>392</v>
@@ -9266,7 +9257,7 @@
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>73.11</v>
+        <v>73.07</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>15</v>
@@ -9277,16 +9268,16 @@
         <v>2022</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>392</v>
@@ -9298,7 +9289,7 @@
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>73.07</v>
+        <v>72.94</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>15</v>
@@ -9309,16 +9300,16 @@
         <v>2022</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>392</v>
@@ -9330,7 +9321,7 @@
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>72.94</v>
+        <v>72.89</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>15</v>
@@ -9341,16 +9332,16 @@
         <v>2022</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="D214" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>392</v>
@@ -9362,7 +9353,7 @@
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>72.89</v>
+        <v>72.57</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>15</v>
@@ -9373,16 +9364,16 @@
         <v>2022</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>392</v>
@@ -9394,7 +9385,7 @@
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>72.57</v>
+        <v>72.23</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>15</v>
@@ -9405,16 +9396,16 @@
         <v>2022</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>392</v>
@@ -9426,7 +9417,7 @@
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>72.23</v>
+        <v>71.96</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>15</v>
@@ -9437,16 +9428,16 @@
         <v>2022</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>392</v>
@@ -9458,7 +9449,7 @@
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>71.96</v>
+        <v>71.83</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>15</v>
@@ -9475,10 +9466,10 @@
         <v>421</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>392</v>
@@ -9490,7 +9481,7 @@
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>71.83</v>
+        <v>71.51</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>15</v>
@@ -9501,16 +9492,16 @@
         <v>2022</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="D219" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E219" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>392</v>
@@ -9522,7 +9513,7 @@
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>71.51</v>
+        <v>71.14</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>15</v>
@@ -9533,16 +9524,16 @@
         <v>2022</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D220" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>392</v>
@@ -9554,7 +9545,7 @@
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>71.14</v>
+        <v>70.25</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>15</v>
@@ -9571,10 +9562,10 @@
         <v>421</v>
       </c>
       <c r="D221" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E221" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>392</v>
@@ -9586,7 +9577,7 @@
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>70.25</v>
+        <v>69.86</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>15</v>
@@ -9597,16 +9588,16 @@
         <v>2022</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="D222" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E222" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>392</v>
@@ -9618,7 +9609,7 @@
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>69.86</v>
+        <v>69.75</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>15</v>
@@ -9635,10 +9626,10 @@
         <v>414</v>
       </c>
       <c r="D223" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E223" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>392</v>
@@ -9650,7 +9641,7 @@
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>69.75</v>
+        <v>69</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>15</v>
@@ -9661,16 +9652,16 @@
         <v>2022</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D224" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E224" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>392</v>
@@ -9682,7 +9673,7 @@
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>69</v>
+        <v>68.14</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>15</v>
@@ -9693,10 +9684,10 @@
         <v>2022</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>472</v>
@@ -9705,16 +9696,16 @@
         <v>473</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>392</v>
+        <v>474</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>393</v>
+        <v>475</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>68.14</v>
+        <v>79.75</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>15</v>
@@ -9728,25 +9719,25 @@
         <v>8</v>
       </c>
       <c r="C226" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F226" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="G226" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="E226" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>79.75</v>
+        <v>79.74</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>15</v>
@@ -9760,25 +9751,25 @@
         <v>8</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D227" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G227" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>79.74</v>
+        <v>79.55</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>15</v>
@@ -9792,25 +9783,25 @@
         <v>8</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D228" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G228" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>79.55</v>
+        <v>79.25</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>15</v>
@@ -9821,10 +9812,10 @@
         <v>2022</v>
       </c>
       <c r="B229" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>483</v>
@@ -9833,16 +9824,16 @@
         <v>484</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>79.25</v>
+        <v>79.16</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>15</v>
@@ -9853,28 +9844,28 @@
         <v>2022</v>
       </c>
       <c r="B230" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C230" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D230" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="E230" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E230" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="F230" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>79.16</v>
+        <v>79.06</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>15</v>
@@ -9885,10 +9876,10 @@
         <v>2022</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>488</v>
@@ -9897,16 +9888,16 @@
         <v>489</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>79.06</v>
+        <v>78.79</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>15</v>
@@ -9917,28 +9908,28 @@
         <v>2022</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D232" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="E232" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="E232" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="F232" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>78.79</v>
+        <v>78.77</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>15</v>
@@ -9949,28 +9940,28 @@
         <v>2022</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G233" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>78.77</v>
+        <v>78.38</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>15</v>
@@ -9981,28 +9972,28 @@
         <v>2022</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D234" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E234" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="E234" s="2" t="s">
-        <v>496</v>
-      </c>
       <c r="F234" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>78.38</v>
+        <v>78.37</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>15</v>
@@ -10013,28 +10004,28 @@
         <v>2022</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C235" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D235" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G235" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>78.37</v>
+        <v>78.33</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>15</v>
@@ -10045,28 +10036,28 @@
         <v>2022</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D236" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E236" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="E236" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="F236" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>78.33</v>
+        <v>78.28</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>15</v>
@@ -10077,28 +10068,28 @@
         <v>2022</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D237" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="E237" s="2" t="s">
-        <v>502</v>
-      </c>
       <c r="F237" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>78.28</v>
+        <v>77.99</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>15</v>
@@ -10109,10 +10100,10 @@
         <v>2022</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>503</v>
@@ -10121,16 +10112,16 @@
         <v>504</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>77.99</v>
+        <v>77.95</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>15</v>
@@ -10141,28 +10132,28 @@
         <v>2022</v>
       </c>
       <c r="B239" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D239" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D239" s="2" t="s">
+      <c r="E239" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="E239" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="F239" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>77.95</v>
+        <v>77.87</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>15</v>
@@ -10176,25 +10167,25 @@
         <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G240" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>77.87</v>
+        <v>77.76</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>15</v>
@@ -10208,25 +10199,25 @@
         <v>8</v>
       </c>
       <c r="C241" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D241" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G241" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>77.76</v>
+        <v>77.74</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>15</v>
@@ -10240,25 +10231,25 @@
         <v>8</v>
       </c>
       <c r="C242" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F242" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D242" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G242" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>77.74</v>
+        <v>77.65</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>15</v>
@@ -10272,25 +10263,25 @@
         <v>8</v>
       </c>
       <c r="C243" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D243" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G243" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>77.65</v>
+        <v>77.57</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>15</v>
@@ -10301,28 +10292,28 @@
         <v>2022</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C244" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F244" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G244" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>77.57</v>
+        <v>77.54</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>15</v>
@@ -10333,28 +10324,28 @@
         <v>2022</v>
       </c>
       <c r="B245" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="D245" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="F245" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>77.54</v>
+        <v>77.48</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>15</v>
@@ -10365,28 +10356,28 @@
         <v>2022</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G246" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>77.48</v>
+        <v>77.4</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>15</v>
@@ -10397,28 +10388,28 @@
         <v>2022</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="D247" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="E247" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="F247" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>77.4</v>
+        <v>77.37</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>15</v>
@@ -10429,22 +10420,22 @@
         <v>2022</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C248" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D248" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G248" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10461,28 +10452,28 @@
         <v>2022</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D249" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E249" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="E249" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="F249" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>77.37</v>
+        <v>77.35</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>15</v>
@@ -10493,28 +10484,28 @@
         <v>2022</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D250" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G250" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>77.35</v>
+        <v>77.21</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>15</v>
@@ -10528,25 +10519,25 @@
         <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D251" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="E251" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="F251" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>77.21</v>
+        <v>77.19</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>15</v>
@@ -10560,19 +10551,19 @@
         <v>9</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D252" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="E252" s="2" t="s">
-        <v>533</v>
-      </c>
       <c r="F252" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10589,28 +10580,28 @@
         <v>2022</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="E253" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="F253" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>77.19</v>
+        <v>76.94</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>15</v>
@@ -10624,25 +10615,25 @@
         <v>8</v>
       </c>
       <c r="C254" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G254" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>76.94</v>
+        <v>76.89</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>15</v>
@@ -10653,28 +10644,28 @@
         <v>2022</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C255" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F255" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D255" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G255" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>76.89</v>
+        <v>76.86</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>15</v>
@@ -10685,28 +10676,28 @@
         <v>2022</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="D256" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E256" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="E256" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="F256" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>76.86</v>
+        <v>76.79</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>15</v>
@@ -10717,28 +10708,28 @@
         <v>2022</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="D257" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E257" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="E257" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="F257" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>76.79</v>
+        <v>76.71</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>15</v>
@@ -10752,25 +10743,25 @@
         <v>8</v>
       </c>
       <c r="C258" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D258" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G258" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>76.71</v>
+        <v>76.59</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>15</v>
@@ -10781,28 +10772,28 @@
         <v>2022</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F259" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D259" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G259" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>76.59</v>
+        <v>76.51</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>15</v>
@@ -10813,28 +10804,28 @@
         <v>2022</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D260" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E260" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E260" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="F260" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>76.51</v>
+        <v>76.47</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>15</v>
@@ -10845,28 +10836,28 @@
         <v>2022</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D261" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E261" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>551</v>
-      </c>
       <c r="F261" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>76.47</v>
+        <v>76.43</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>15</v>
@@ -10880,25 +10871,25 @@
         <v>9</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D262" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E262" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="E262" s="2" t="s">
-        <v>553</v>
-      </c>
       <c r="F262" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>76.43</v>
+        <v>76.4</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>15</v>
@@ -10912,25 +10903,25 @@
         <v>9</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D263" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E263" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="E263" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="F263" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>76.4</v>
+        <v>76.3</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>15</v>
@@ -10941,22 +10932,22 @@
         <v>2022</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D264" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E264" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="E264" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="F264" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -10976,25 +10967,25 @@
         <v>14</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D265" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E265" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="E265" s="2" t="s">
-        <v>559</v>
-      </c>
       <c r="F265" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>76.3</v>
+        <v>76.17</v>
       </c>
       <c r="J265" s="2" t="s">
         <v>15</v>
@@ -11008,25 +10999,25 @@
         <v>14</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D266" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="E266" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="F266" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>76.17</v>
+        <v>76.13</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>15</v>
@@ -11037,28 +11028,28 @@
         <v>2022</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D267" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="E267" s="2" t="s">
-        <v>563</v>
-      </c>
       <c r="F267" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>76.13</v>
+        <v>75.98</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>15</v>
@@ -11069,28 +11060,28 @@
         <v>2022</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D268" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E268" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="E268" s="2" t="s">
-        <v>565</v>
-      </c>
       <c r="F268" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>75.98</v>
+        <v>75.92</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>15</v>
@@ -11101,22 +11092,22 @@
         <v>2022</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C269" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F269" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D269" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G269" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11133,28 +11124,28 @@
         <v>2022</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D270" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E270" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="F270" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>75.92</v>
+        <v>75.91</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>15</v>
@@ -11168,25 +11159,25 @@
         <v>9</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D271" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E271" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E271" s="2" t="s">
-        <v>571</v>
-      </c>
       <c r="F271" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>75.91</v>
+        <v>75.89</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>15</v>
@@ -11197,28 +11188,28 @@
         <v>2022</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D272" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E272" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E272" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="F272" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>75.89</v>
+        <v>75.79</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>15</v>
@@ -11229,28 +11220,28 @@
         <v>2022</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G273" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>75.79</v>
+        <v>75.78</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>15</v>
@@ -11261,28 +11252,28 @@
         <v>2022</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D274" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E274" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="E274" s="2" t="s">
-        <v>577</v>
-      </c>
       <c r="F274" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>75.78</v>
+        <v>75.66</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>15</v>
@@ -11293,28 +11284,28 @@
         <v>2022</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C275" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D275" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G275" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>75.66</v>
+        <v>75.48</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>15</v>
@@ -11325,28 +11316,28 @@
         <v>2022</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D276" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E276" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="E276" s="2" t="s">
-        <v>581</v>
-      </c>
       <c r="F276" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>75.48</v>
+        <v>75.45</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>15</v>
@@ -11357,28 +11348,28 @@
         <v>2022</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="D277" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E277" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="E277" s="2" t="s">
-        <v>583</v>
-      </c>
       <c r="F277" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>75.45</v>
+        <v>75.27</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>15</v>
@@ -11389,28 +11380,28 @@
         <v>2022</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C278" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D278" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G278" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>75.27</v>
+        <v>75.26</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>15</v>
@@ -11421,28 +11412,28 @@
         <v>2022</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="D279" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E279" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="E279" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="F279" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>75.26</v>
+        <v>75.24</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>15</v>
@@ -11453,22 +11444,22 @@
         <v>2022</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C280" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D280" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F280" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G280" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11485,28 +11476,28 @@
         <v>2022</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="D281" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E281" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="E281" s="2" t="s">
-        <v>591</v>
-      </c>
       <c r="F281" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>75.24</v>
+        <v>75.22</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>15</v>
@@ -11517,28 +11508,28 @@
         <v>2022</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C282" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F282" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D282" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G282" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>75.22</v>
+        <v>75.21</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>15</v>
@@ -11549,28 +11540,28 @@
         <v>2022</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="D283" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E283" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="E283" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="F283" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>75.21</v>
+        <v>75.19</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>15</v>
@@ -11581,28 +11572,28 @@
         <v>2022</v>
       </c>
       <c r="B284" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C284" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D284" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G284" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>75.19</v>
+        <v>74.95</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>15</v>
@@ -11613,28 +11604,28 @@
         <v>2022</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D285" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E285" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="E285" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="F285" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>74.95</v>
+        <v>74.93</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>15</v>
@@ -11645,28 +11636,28 @@
         <v>2022</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D286" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E286" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="E286" s="2" t="s">
-        <v>601</v>
-      </c>
       <c r="F286" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>74.93</v>
+        <v>74.92</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>15</v>
@@ -11677,28 +11668,28 @@
         <v>2022</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D287" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E287" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="E287" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="F287" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>74.92</v>
+        <v>74.86</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>15</v>
@@ -11709,28 +11700,28 @@
         <v>2022</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D288" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E288" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="E288" s="2" t="s">
-        <v>605</v>
-      </c>
       <c r="F288" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>74.86</v>
+        <v>74.78</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>15</v>
@@ -11741,28 +11732,28 @@
         <v>2022</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C289" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D289" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G289" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>74.78</v>
+        <v>74.72</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>15</v>
@@ -11773,28 +11764,28 @@
         <v>2022</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D290" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E290" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="E290" s="2" t="s">
-        <v>609</v>
-      </c>
       <c r="F290" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>74.72</v>
+        <v>74.67</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>15</v>
@@ -11805,28 +11796,28 @@
         <v>2022</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D291" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E291" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="E291" s="2" t="s">
-        <v>611</v>
-      </c>
       <c r="F291" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>74.67</v>
+        <v>74.6</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>15</v>
@@ -11837,28 +11828,28 @@
         <v>2022</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="D292" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E292" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="E292" s="2" t="s">
-        <v>613</v>
-      </c>
       <c r="F292" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>74.6</v>
+        <v>74.37</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>15</v>
@@ -11869,28 +11860,28 @@
         <v>2022</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D293" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E293" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="F293" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>74.37</v>
+        <v>74.31</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>15</v>
@@ -11904,25 +11895,25 @@
         <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D294" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E294" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="E294" s="2" t="s">
-        <v>617</v>
-      </c>
       <c r="F294" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>74.31</v>
+        <v>74.22</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>15</v>
@@ -11933,28 +11924,28 @@
         <v>2022</v>
       </c>
       <c r="B295" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D295" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E295" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E295" s="2" t="s">
-        <v>619</v>
-      </c>
       <c r="F295" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>74.22</v>
+        <v>74.15</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>15</v>
@@ -11965,28 +11956,28 @@
         <v>2022</v>
       </c>
       <c r="B296" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="F296" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D296" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G296" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>74.15</v>
+        <v>74.01</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>15</v>
@@ -11997,28 +11988,28 @@
         <v>2022</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D297" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E297" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="E297" s="2" t="s">
-        <v>623</v>
-      </c>
       <c r="F297" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>74.01</v>
+        <v>73.97</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>15</v>
@@ -12029,28 +12020,28 @@
         <v>2022</v>
       </c>
       <c r="B298" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="F298" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D298" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G298" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>73.97</v>
+        <v>73.84</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>15</v>
@@ -12064,25 +12055,25 @@
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D299" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E299" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="E299" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="F299" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>73.84</v>
+        <v>73.83</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>15</v>
@@ -12096,25 +12087,25 @@
         <v>10</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D300" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E300" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="E300" s="2" t="s">
-        <v>629</v>
-      </c>
       <c r="F300" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>73.83</v>
+        <v>73.72</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>15</v>
@@ -12125,28 +12116,28 @@
         <v>2022</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="D301" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E301" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="E301" s="2" t="s">
-        <v>631</v>
-      </c>
       <c r="F301" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>73.72</v>
+        <v>73.66</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>15</v>
@@ -12157,28 +12148,28 @@
         <v>2022</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="E302" s="2" t="s">
-        <v>633</v>
-      </c>
       <c r="F302" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>73.66</v>
+        <v>73.62</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>15</v>
@@ -12189,28 +12180,28 @@
         <v>2022</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C303" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F303" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D303" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G303" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>73.62</v>
+        <v>73.61</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>15</v>
@@ -12221,28 +12212,28 @@
         <v>2022</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D304" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E304" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E304" s="2" t="s">
-        <v>637</v>
-      </c>
       <c r="F304" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>73.61</v>
+        <v>73.58</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>15</v>
@@ -12256,25 +12247,25 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D305" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E305" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="F305" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>73.58</v>
+        <v>73.43</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>15</v>
@@ -12285,28 +12276,28 @@
         <v>2022</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D306" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E306" s="2" t="s">
-        <v>641</v>
-      </c>
       <c r="F306" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>73.43</v>
+        <v>73.34</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>15</v>
@@ -12317,28 +12308,28 @@
         <v>2022</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>643</v>
+        <v>502</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>73.34</v>
+        <v>73.33</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>15</v>
@@ -12349,28 +12340,28 @@
         <v>2022</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>505</v>
+        <v>643</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>73.33</v>
+        <v>73.31</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>15</v>
@@ -12381,28 +12372,28 @@
         <v>2022</v>
       </c>
       <c r="B309" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D309" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E309" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="E309" s="2" t="s">
-        <v>646</v>
-      </c>
       <c r="F309" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>73.31</v>
+        <v>73.29</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>15</v>
@@ -12413,28 +12404,28 @@
         <v>2022</v>
       </c>
       <c r="B310" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D310" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E310" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="E310" s="2" t="s">
-        <v>648</v>
-      </c>
       <c r="F310" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>73.29</v>
+        <v>73.28</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>15</v>
@@ -12445,28 +12436,28 @@
         <v>2022</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D311" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E311" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="E311" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="F311" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>73.28</v>
+        <v>73.24</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>15</v>
@@ -12477,28 +12468,28 @@
         <v>2022</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C312" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F312" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D312" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G312" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>73.24</v>
+        <v>73.2</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>15</v>
@@ -12509,28 +12500,28 @@
         <v>2022</v>
       </c>
       <c r="B313" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D313" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="E313" s="2" t="s">
-        <v>654</v>
-      </c>
       <c r="F313" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>73.2</v>
+        <v>73.19</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>15</v>
@@ -12541,28 +12532,28 @@
         <v>2022</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D314" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="E314" s="2" t="s">
-        <v>656</v>
-      </c>
       <c r="F314" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>73.19</v>
+        <v>73.1</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>15</v>
@@ -12573,28 +12564,28 @@
         <v>2022</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D315" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E315" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="E315" s="2" t="s">
-        <v>658</v>
-      </c>
       <c r="F315" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>73.1</v>
+        <v>73.08</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>15</v>
@@ -12605,28 +12596,28 @@
         <v>2022</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="D316" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E316" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="E316" s="2" t="s">
-        <v>660</v>
-      </c>
       <c r="F316" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>73.08</v>
+        <v>72.93</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>15</v>
@@ -12637,28 +12628,28 @@
         <v>2022</v>
       </c>
       <c r="B317" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="D317" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="E317" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="F317" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>72.93</v>
+        <v>72.83</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>15</v>
@@ -12672,25 +12663,25 @@
         <v>8</v>
       </c>
       <c r="C318" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F318" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D318" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G318" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>72.83</v>
+        <v>72.41</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>15</v>
@@ -12701,28 +12692,28 @@
         <v>2022</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F319" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D319" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="E319" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="G319" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>72.41</v>
+        <v>72.38</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>15</v>
@@ -12736,25 +12727,25 @@
         <v>10</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D320" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E320" s="2" t="s">
-        <v>668</v>
-      </c>
       <c r="F320" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>72.38</v>
+        <v>72.37</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>15</v>
@@ -12768,25 +12759,25 @@
         <v>10</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D321" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E321" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="E321" s="2" t="s">
-        <v>670</v>
-      </c>
       <c r="F321" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>72.37</v>
+        <v>72.04</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>15</v>
@@ -12800,25 +12791,25 @@
         <v>10</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D322" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E322" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="E322" s="2" t="s">
-        <v>672</v>
-      </c>
       <c r="F322" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>72.04</v>
+        <v>71.55</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>15</v>
@@ -12832,25 +12823,25 @@
         <v>10</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D323" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E323" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="E323" s="2" t="s">
-        <v>674</v>
-      </c>
       <c r="F323" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>71.55</v>
+        <v>71.54</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>15</v>
@@ -12864,25 +12855,25 @@
         <v>10</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D324" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E324" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="E324" s="2" t="s">
-        <v>676</v>
-      </c>
       <c r="F324" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>71.54</v>
+        <v>71.12</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>15</v>
@@ -12896,25 +12887,25 @@
         <v>10</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D325" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E325" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="E325" s="2" t="s">
-        <v>678</v>
-      </c>
       <c r="F325" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>71.12</v>
+        <v>70.86</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>15</v>
@@ -12928,25 +12919,25 @@
         <v>10</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D326" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="E326" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="E326" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="F326" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>70.86</v>
+        <v>70.64</v>
       </c>
       <c r="J326" s="2" t="s">
         <v>15</v>
@@ -12957,28 +12948,28 @@
         <v>2022</v>
       </c>
       <c r="B327" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D327" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E327" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="E327" s="2" t="s">
-        <v>682</v>
-      </c>
       <c r="F327" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>70.64</v>
+        <v>70.62</v>
       </c>
       <c r="J327" s="2" t="s">
         <v>15</v>
@@ -12992,25 +12983,25 @@
         <v>9</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D328" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="E328" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="E328" s="2" t="s">
-        <v>684</v>
-      </c>
       <c r="F328" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>70.62</v>
+        <v>69.37</v>
       </c>
       <c r="J328" s="2" t="s">
         <v>15</v>
@@ -13021,28 +13012,28 @@
         <v>2022</v>
       </c>
       <c r="B329" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="D329" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E329" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="E329" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="F329" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>69.37</v>
+        <v>68.91</v>
       </c>
       <c r="J329" s="2" t="s">
         <v>15</v>
@@ -13053,67 +13044,35 @@
         <v>2022</v>
       </c>
       <c r="B330" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>505</v>
+        <v>482</v>
       </c>
       <c r="D330" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="E330" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="E330" s="2" t="s">
-        <v>688</v>
-      </c>
       <c r="F330" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>68.91</v>
+        <v>68.59</v>
       </c>
       <c r="J330" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B331" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C331" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D331" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="E331" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="F331" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="G331" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="H331" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I331" s="2" t="n">
-        <v>68.59</v>
-      </c>
-      <c r="J331" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J331"/>
+  <autoFilter ref="A1:J330"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -13130,7 +13089,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -13138,50 +13097,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -13203,21 +13162,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13226,7 +13185,7 @@
         <v>2022</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2022.xlsx
@@ -2089,7 +2089,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:48</t>
+    <t xml:space="preserve">2026-09-08 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
